--- a/Result/profitability/8210.xlsx
+++ b/Result/profitability/8210.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.3</v>
       </c>
       <c r="M2" t="n">
-        <v>6.1775</v>
+        <v>6.8975</v>
       </c>
       <c r="N2" t="n">
-        <v>28.81</v>
+        <v>29.28625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.16</v>
       </c>
       <c r="M3" t="n">
-        <v>5.53</v>
+        <v>6.428750000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>27.57125</v>
+        <v>28.56</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.63</v>
       </c>
       <c r="M4" t="n">
-        <v>5.120000000000001</v>
+        <v>5.81625</v>
       </c>
       <c r="N4" t="n">
-        <v>27.55875</v>
+        <v>28.03125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>4.366250000000001</v>
+        <v>4.895</v>
       </c>
       <c r="N5" t="n">
-        <v>26.145</v>
+        <v>26.48625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.34</v>
       </c>
       <c r="M6" t="n">
-        <v>3.55</v>
+        <v>3.93625</v>
       </c>
       <c r="N6" t="n">
-        <v>25.3625</v>
+        <v>25.5275</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.61</v>
       </c>
       <c r="M7" t="n">
-        <v>2.625</v>
+        <v>2.92125</v>
       </c>
       <c r="N7" t="n">
-        <v>24.79125</v>
+        <v>25.17875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.13</v>
       </c>
       <c r="M8" t="n">
-        <v>1.675</v>
+        <v>1.72125</v>
       </c>
       <c r="N8" t="n">
-        <v>24.24375</v>
+        <v>24.22125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>7821</v>
+      </c>
+      <c r="D75" t="n">
+        <v>5268</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2553</v>
+      </c>
+      <c r="F75" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1926</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>24.63%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-22</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1904</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1383</v>
+      </c>
+      <c r="L75" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="M75" t="n">
+        <v>7.527500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>29.84125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.3699999999999992</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.0344827586206895</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.1799999999999997</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.005482790130977744</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.6157205240174672</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.729999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.09124331550802123</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
